--- a/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 25,86</t>
+          <t>18,47; 25,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,1; 35,84</t>
+          <t>27,12; 36,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,88; 34,71</t>
+          <t>25,52; 34,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,55; 34,81</t>
+          <t>18,41; 34,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,27; 41,02</t>
+          <t>31,84; 40,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,82; 46,05</t>
+          <t>36,31; 45,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,41; 39,03</t>
+          <t>29,83; 39,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 31,72</t>
+          <t>17,87; 31,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,08; 32,11</t>
+          <t>26,23; 31,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,06; 39,46</t>
+          <t>32,72; 39,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,8; 35,43</t>
+          <t>28,98; 35,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,1; 31,18</t>
+          <t>19,78; 30,79</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,18; 30,78</t>
+          <t>24,33; 30,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,87; 42,25</t>
+          <t>34,82; 42,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,06; 32,99</t>
+          <t>24,67; 32,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 28,32</t>
+          <t>17,48; 27,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,79; 47,41</t>
+          <t>39,41; 48,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,08; 51,73</t>
+          <t>43,52; 51,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,66; 44,08</t>
+          <t>36,18; 44,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 24,42</t>
+          <t>12,08; 25,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,06; 37,3</t>
+          <t>32,4; 37,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39,87; 45,49</t>
+          <t>40,16; 45,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,46; 36,71</t>
+          <t>31,25; 36,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,77; 24,9</t>
+          <t>16,25; 24,97</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,74; 37,5</t>
+          <t>29,76; 37,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,96; 44,61</t>
+          <t>36,88; 44,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,95; 37,19</t>
+          <t>30,08; 37,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 24,12</t>
+          <t>17,51; 24,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,81; 54,97</t>
+          <t>47,61; 55,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,28; 61,34</t>
+          <t>53,07; 61,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,94; 51,36</t>
+          <t>44,2; 51,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,56; 27,53</t>
+          <t>17,93; 27,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,19; 45,5</t>
+          <t>40,15; 45,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,03; 51,9</t>
+          <t>46,4; 51,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,74; 43,37</t>
+          <t>37,57; 43,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 24,81</t>
+          <t>19,33; 25,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,76; 52,37</t>
+          <t>42,77; 52,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,73; 54,26</t>
+          <t>45,57; 53,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,83; 56,1</t>
+          <t>47,43; 56,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 31,72</t>
+          <t>10,01; 31,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,47; 67,73</t>
+          <t>58,97; 67,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,13; 74,53</t>
+          <t>66,92; 74,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,28; 62,96</t>
+          <t>55,23; 63,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,17; 37,95</t>
+          <t>28,6; 38,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,18; 58,38</t>
+          <t>51,76; 58,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,3; 63,53</t>
+          <t>57,8; 63,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,86; 58,2</t>
+          <t>52,6; 58,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 33,32</t>
+          <t>17,44; 33,5</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,25; 75,22</t>
+          <t>66,16; 75,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,56; 80,26</t>
+          <t>71,6; 79,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,17; 68,52</t>
+          <t>58,98; 68,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,52; 48,07</t>
+          <t>40,17; 47,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,13; 81,24</t>
+          <t>73,72; 81,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,82; 89,39</t>
+          <t>82,63; 89,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,2; 82,62</t>
+          <t>74,6; 82,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,4; 52,65</t>
+          <t>46,51; 53,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,77; 77,13</t>
+          <t>70,94; 77,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77,97; 83,89</t>
+          <t>77,85; 83,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68,31; 74,57</t>
+          <t>68,05; 74,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,2; 49,15</t>
+          <t>44,44; 49,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,49; 81,35</t>
+          <t>71,98; 81,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,27; 95,45</t>
+          <t>89,09; 95,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,68; 91,04</t>
+          <t>83,01; 90,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42,69; 51,11</t>
+          <t>43,22; 51,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84,98; 91,48</t>
+          <t>84,9; 91,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91,25; 96,35</t>
+          <t>91,2; 96,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,6; 92,0</t>
+          <t>85,24; 92,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58,12; 88,44</t>
+          <t>58,28; 87,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80,15; 85,86</t>
+          <t>80,02; 85,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91,58; 95,38</t>
+          <t>91,08; 95,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85,38; 90,4</t>
+          <t>85,5; 90,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52,62; 79,95</t>
+          <t>52,72; 80,56</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,3; 91,0</t>
+          <t>81,82; 91,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92,03; 97,47</t>
+          <t>91,57; 97,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,6; 95,72</t>
+          <t>89,69; 95,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58,89; 68,38</t>
+          <t>58,67; 67,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,84; 92,95</t>
+          <t>85,95; 93,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,02; 98,56</t>
+          <t>94,8; 98,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,62; 98,04</t>
+          <t>93,58; 98,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,5; 70,18</t>
+          <t>63,46; 69,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,85; 91,25</t>
+          <t>85,6; 91,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94,54; 97,61</t>
+          <t>94,6; 97,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93,07; 96,44</t>
+          <t>93,04; 96,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,04; 68,76</t>
+          <t>62,93; 67,97</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,58; 46,34</t>
+          <t>42,58; 46,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,23; 55,7</t>
+          <t>52,17; 55,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,97; 51,55</t>
+          <t>48,0; 51,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,38; 35,18</t>
+          <t>24,61; 35,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,74; 62,17</t>
+          <t>58,8; 62,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,95; 69,23</t>
+          <t>65,88; 69,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,63; 62,93</t>
+          <t>59,8; 62,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,18; 53,57</t>
+          <t>38,04; 53,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,27; 53,79</t>
+          <t>51,26; 53,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59,7; 62,11</t>
+          <t>59,72; 62,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54,38; 56,82</t>
+          <t>54,42; 56,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,68; 42,82</t>
+          <t>33,86; 42,62</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91433; 127750</t>
+          <t>91256; 128352</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123093; 162770</t>
+          <t>123184; 165010</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104365; 145598</t>
+          <t>107039; 145725</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74207; 139246</t>
+          <t>73647; 137071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>150859; 191751</t>
+          <t>148827; 189356</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>158409; 198141</t>
+          <t>156233; 197430</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120352; 154476</t>
+          <t>118052; 155643</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55945; 99341</t>
+          <t>55979; 97367</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>250750; 308726</t>
+          <t>252168; 306593</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>292377; 348970</t>
+          <t>289400; 349107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234816; 288828</t>
+          <t>236252; 288592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>143356; 222345</t>
+          <t>141077; 219613</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>177822; 226413</t>
+          <t>178912; 227543</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>239590; 290279</t>
+          <t>239270; 293360</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147987; 194818</t>
+          <t>145675; 190982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73994; 119949</t>
+          <t>74033; 118489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>248867; 296557</t>
+          <t>246486; 300908</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>262907; 315688</t>
+          <t>265574; 316133</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>200952; 248405</t>
+          <t>203871; 250822</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60670; 125077</t>
+          <t>61878; 128697</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>436318; 507626</t>
+          <t>440957; 511440</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>517286; 590172</t>
+          <t>520991; 591151</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>363084; 423663</t>
+          <t>360599; 424240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>147554; 232951</t>
+          <t>152030; 233633</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>189927; 239479</t>
+          <t>190037; 239704</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>252018; 304209</t>
+          <t>251479; 305848</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>200377; 248854</t>
+          <t>201296; 250081</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89443; 129382</t>
+          <t>93892; 131896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>329766; 379142</t>
+          <t>328385; 380401</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>378769; 436003</t>
+          <t>377266; 435618</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>290588; 339675</t>
+          <t>292317; 340798</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>109890; 163000</t>
+          <t>106163; 165207</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>533865; 604381</t>
+          <t>533408; 606642</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>641080; 722806</t>
+          <t>646264; 723837</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>502184; 577069</t>
+          <t>499876; 572595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>212197; 279901</t>
+          <t>218069; 282864</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>221986; 271891</t>
+          <t>222053; 271745</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>281053; 333502</t>
+          <t>280090; 331090</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>309020; 362434</t>
+          <t>306405; 362341</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86602; 281597</t>
+          <t>88841; 281689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>306650; 349267</t>
+          <t>304049; 346266</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>413677; 459276</t>
+          <t>412389; 459808</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>358781; 408657</t>
+          <t>358495; 409580</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>207982; 270572</t>
+          <t>203870; 271162</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>539961; 604149</t>
+          <t>535624; 602561</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>705278; 781942</t>
+          <t>711396; 783372</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>684552; 753721</t>
+          <t>681190; 752920</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>257140; 533278</t>
+          <t>279231; 536158</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>256194; 290891</t>
+          <t>255830; 291386</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>307313; 344657</t>
+          <t>307471; 342937</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>282765; 327472</t>
+          <t>281898; 327353</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227409; 269768</t>
+          <t>225426; 268867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>295418; 328197</t>
+          <t>297803; 329005</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>370872; 400274</t>
+          <t>370000; 401725</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>368652; 410506</t>
+          <t>370652; 410010</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>254204; 288488</t>
+          <t>254810; 290551</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>559575; 609887</t>
+          <t>560896; 608935</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>683963; 735899</t>
+          <t>682927; 733681</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>665893; 726854</t>
+          <t>663331; 727680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>490256; 545195</t>
+          <t>492879; 548653</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>209168; 238012</t>
+          <t>210607; 238802</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>276537; 295675</t>
+          <t>275984; 295366</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>279764; 304371</t>
+          <t>277538; 303031</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157174; 188153</t>
+          <t>159126; 189331</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>291414; 313717</t>
+          <t>291167; 313599</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>323020; 341077</t>
+          <t>322836; 341260</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>323356; 347551</t>
+          <t>322016; 348230</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>353602; 538015</t>
+          <t>354558; 534162</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>509392; 545660</t>
+          <t>508545; 545501</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607860; 633087</t>
+          <t>604604; 632646</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607957; 643698</t>
+          <t>608813; 644600</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>513816; 780780</t>
+          <t>514853; 786726</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>172740; 191000</t>
+          <t>171716; 191035</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>229931; 243521</t>
+          <t>228793; 243440</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230263; 246004</t>
+          <t>230513; 245677</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>166518; 193348</t>
+          <t>165908; 192139</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>286625; 310352</t>
+          <t>286994; 311341</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>369596; 383361</t>
+          <t>368755; 383400</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>374646; 392338</t>
+          <t>374482; 392297</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>270419; 298859</t>
+          <t>270246; 297632</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>466842; 496230</t>
+          <t>465485; 496329</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>603976; 623579</t>
+          <t>604345; 623912</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>611646; 633801</t>
+          <t>611449; 633949</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>446703; 487261</t>
+          <t>445883; 481664</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1395018; 1518207</t>
+          <t>1395138; 1511228</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1789667; 1908688</t>
+          <t>1787734; 1905940</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1628133; 1749665</t>
+          <t>1629433; 1743343</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>878030; 1217031</t>
+          <t>851461; 1212100</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1984896; 2100982</t>
+          <t>1987034; 2098254</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2346785; 2463521</t>
+          <t>2344188; 2461200</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2113439; 2230684</t>
+          <t>2119804; 2232713</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1417449; 1988813</t>
+          <t>1412102; 1968520</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3412677; 3580049</t>
+          <t>3411780; 3578155</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4170243; 4338258</t>
+          <t>4171772; 4338291</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3773554; 3942718</t>
+          <t>3775991; 3938798</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2415351; 3070970</t>
+          <t>2428411; 3056824</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 25,98</t>
+          <t>18,62; 25,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,12; 36,33</t>
+          <t>27,41; 36,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,52; 34,74</t>
+          <t>25,29; 34,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,41; 34,27</t>
+          <t>14,36; 27,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,84; 40,5</t>
+          <t>32,23; 41,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,31; 45,89</t>
+          <t>36,25; 45,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,83; 39,33</t>
+          <t>29,98; 38,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,87; 31,09</t>
+          <t>16,71; 29,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,23; 31,89</t>
+          <t>26,57; 31,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,72; 39,47</t>
+          <t>33,0; 39,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,98; 35,4</t>
+          <t>28,43; 35,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,78; 30,79</t>
+          <t>17,5; 26,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,33; 30,94</t>
+          <t>24,59; 31,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,82; 42,7</t>
+          <t>34,96; 42,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,67; 32,34</t>
+          <t>24,77; 32,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 27,98</t>
+          <t>16,63; 26,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,41; 48,11</t>
+          <t>39,16; 47,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,52; 51,8</t>
+          <t>43,41; 51,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,18; 44,51</t>
+          <t>35,86; 43,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 25,13</t>
+          <t>18,32; 25,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,4; 37,58</t>
+          <t>32,33; 37,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40,16; 45,57</t>
+          <t>39,88; 45,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,25; 36,76</t>
+          <t>31,61; 36,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,25; 24,97</t>
+          <t>18,28; 24,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,76; 37,53</t>
+          <t>29,57; 37,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,88; 44,85</t>
+          <t>37,14; 45,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,08; 37,38</t>
+          <t>29,67; 37,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 24,59</t>
+          <t>16,62; 23,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,61; 55,15</t>
+          <t>47,64; 55,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,07; 61,28</t>
+          <t>53,15; 60,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,2; 51,53</t>
+          <t>44,13; 51,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 27,91</t>
+          <t>22,6; 28,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,15; 45,67</t>
+          <t>39,98; 45,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,4; 51,97</t>
+          <t>46,31; 51,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,57; 43,04</t>
+          <t>37,9; 43,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,07</t>
+          <t>20,56; 24,73</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,77; 52,34</t>
+          <t>42,5; 51,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,57; 53,87</t>
+          <t>45,55; 54,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,43; 56,09</t>
+          <t>47,44; 55,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 31,73</t>
+          <t>26,62; 33,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,97; 67,15</t>
+          <t>59,36; 67,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,92; 74,62</t>
+          <t>66,89; 74,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,23; 63,1</t>
+          <t>54,86; 62,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,6; 38,04</t>
+          <t>32,83; 38,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,76; 58,23</t>
+          <t>52,0; 58,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,8; 63,65</t>
+          <t>57,58; 63,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,6; 58,13</t>
+          <t>52,55; 57,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,44; 33,5</t>
+          <t>30,74; 35,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,16; 75,35</t>
+          <t>66,35; 75,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,6; 79,86</t>
+          <t>71,24; 79,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,98; 68,5</t>
+          <t>59,44; 68,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,17; 47,91</t>
+          <t>38,91; 46,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,72; 81,44</t>
+          <t>73,1; 81,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,63; 89,71</t>
+          <t>82,81; 89,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,6; 82,52</t>
+          <t>74,25; 82,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,51; 53,03</t>
+          <t>46,43; 52,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,94; 77,01</t>
+          <t>71,05; 77,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77,85; 83,64</t>
+          <t>77,97; 83,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68,05; 74,65</t>
+          <t>68,16; 74,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,44; 49,47</t>
+          <t>43,87; 48,95</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,98; 81,62</t>
+          <t>71,75; 81,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,09; 95,35</t>
+          <t>89,14; 95,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,01; 90,64</t>
+          <t>83,04; 90,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,22; 51,43</t>
+          <t>42,29; 50,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84,9; 91,45</t>
+          <t>85,03; 91,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91,2; 96,4</t>
+          <t>91,57; 96,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,24; 92,18</t>
+          <t>85,15; 92,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58,28; 87,8</t>
+          <t>55,92; 62,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80,02; 85,84</t>
+          <t>80,29; 86,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91,08; 95,31</t>
+          <t>91,4; 95,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85,5; 90,52</t>
+          <t>85,38; 90,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52,72; 80,56</t>
+          <t>50,42; 56,0</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>81,82; 91,02</t>
+          <t>81,62; 90,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>91,57; 97,43</t>
+          <t>92,06; 97,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,69; 95,6</t>
+          <t>89,72; 95,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58,67; 67,95</t>
+          <t>58,57; 68,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,95; 93,24</t>
+          <t>85,77; 92,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,8; 98,57</t>
+          <t>94,65; 98,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,58; 98,03</t>
+          <t>93,27; 97,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,46; 69,89</t>
+          <t>62,98; 69,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,6; 91,27</t>
+          <t>85,99; 91,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94,6; 97,66</t>
+          <t>94,35; 97,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93,04; 96,47</t>
+          <t>93,02; 96,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,93; 67,97</t>
+          <t>62,42; 67,75</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,58; 46,12</t>
+          <t>42,75; 46,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,17; 55,62</t>
+          <t>51,99; 55,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48,0; 51,36</t>
+          <t>47,85; 51,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,61; 35,03</t>
+          <t>31,32; 34,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,8; 62,09</t>
+          <t>58,68; 61,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,88; 69,17</t>
+          <t>65,86; 69,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,8; 62,99</t>
+          <t>59,57; 62,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,04; 53,03</t>
+          <t>38,36; 41,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,26; 53,76</t>
+          <t>51,31; 53,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59,72; 62,11</t>
+          <t>59,62; 62,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54,42; 56,76</t>
+          <t>54,43; 56,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,86; 42,62</t>
+          <t>35,31; 37,64</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103437</t>
+          <t>83223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74660</t>
+          <t>82561</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>178097</t>
+          <t>165784</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91256; 128352</t>
+          <t>91985; 127017</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123184; 165010</t>
+          <t>124490; 163616</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107039; 145725</t>
+          <t>106069; 144793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73647; 137071</t>
+          <t>58540; 112036</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>148827; 189356</t>
+          <t>150687; 193048</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>156233; 197430</t>
+          <t>155975; 196184</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>118052; 155643</t>
+          <t>118646; 154134</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55979; 97367</t>
+          <t>60582; 105128</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>252168; 306593</t>
+          <t>255463; 306021</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289400; 349107</t>
+          <t>291849; 350123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>236252; 288592</t>
+          <t>231751; 287935</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>141077; 219613</t>
+          <t>134791; 204494</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95938</t>
+          <t>99973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>100977</t>
+          <t>109218</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>196915</t>
+          <t>209192</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>178912; 227543</t>
+          <t>180843; 227973</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>239270; 293360</t>
+          <t>240174; 291682</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>145675; 190982</t>
+          <t>146280; 190379</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74033; 118489</t>
+          <t>79298; 124491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>246486; 300908</t>
+          <t>244944; 296054</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>265574; 316133</t>
+          <t>264883; 313605</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>203871; 250822</t>
+          <t>202115; 247449</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61878; 128697</t>
+          <t>91909; 129288</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>440957; 511440</t>
+          <t>439961; 508667</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>520991; 591151</t>
+          <t>517434; 588107</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>360599; 424240</t>
+          <t>364820; 425889</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>152030; 233633</t>
+          <t>178861; 239178</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110297</t>
+          <t>123071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>142068</t>
+          <t>158176</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>252365</t>
+          <t>281247</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>190037; 239704</t>
+          <t>188875; 237957</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>251479; 305848</t>
+          <t>253277; 307185</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>201296; 250081</t>
+          <t>198542; 250507</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93892; 131896</t>
+          <t>103179; 142858</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>328385; 380401</t>
+          <t>328624; 379396</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>377266; 435618</t>
+          <t>377832; 432002</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>292317; 340798</t>
+          <t>291839; 340489</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>106163; 165207</t>
+          <t>140838; 177174</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>533408; 606642</t>
+          <t>531057; 605935</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>646264; 723837</t>
+          <t>644961; 721484</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>499876; 572595</t>
+          <t>504296; 576983</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>218069; 282864</t>
+          <t>255788; 307664</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194400</t>
+          <t>209883</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>246553</t>
+          <t>263262</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>473145</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>222053; 271745</t>
+          <t>220660; 268461</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>280090; 331090</t>
+          <t>279954; 333256</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>306405; 362341</t>
+          <t>306475; 360355</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88841; 281689</t>
+          <t>186479; 238021</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>304049; 346266</t>
+          <t>306104; 348783</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>412389; 459808</t>
+          <t>412184; 460113</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>358495; 409580</t>
+          <t>356075; 407706</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>203870; 271162</t>
+          <t>241941; 282356</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>535624; 602561</t>
+          <t>538133; 602614</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711396; 783372</t>
+          <t>708757; 779917</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>681190; 752920</t>
+          <t>680637; 750975</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>279231; 536158</t>
+          <t>441939; 504260</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>247077</t>
+          <t>260866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>272289</t>
+          <t>301859</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>519366</t>
+          <t>562726</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>255830; 291386</t>
+          <t>256596; 292789</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>307471; 342937</t>
+          <t>305921; 342907</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>281898; 327353</t>
+          <t>284094; 326517</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225426; 268867</t>
+          <t>237119; 284947</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>297803; 329005</t>
+          <t>295301; 328300</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>370000; 401725</t>
+          <t>370806; 400615</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>370652; 410010</t>
+          <t>368906; 410255</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>254810; 290551</t>
+          <t>282713; 321582</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>560896; 608935</t>
+          <t>561809; 610627</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>682927; 733681</t>
+          <t>683946; 732884</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>663331; 727680</t>
+          <t>664408; 723752</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>492879; 548653</t>
+          <t>534478; 596354</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173558</t>
+          <t>189240</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>443732</t>
+          <t>260916</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>617290</t>
+          <t>450155</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>210607; 238802</t>
+          <t>209933; 238314</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>275984; 295366</t>
+          <t>276145; 295821</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>277538; 303031</t>
+          <t>277628; 302649</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>159126; 189331</t>
+          <t>172157; 206063</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>291167; 313599</t>
+          <t>291603; 314592</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>322836; 341260</t>
+          <t>324165; 341990</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>322016; 348230</t>
+          <t>321662; 347705</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>354558; 534162</t>
+          <t>245590; 276126</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>508545; 545501</t>
+          <t>510264; 546768</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>604604; 632646</t>
+          <t>606725; 633511</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608813; 644600</t>
+          <t>607951; 644970</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>514853; 786726</t>
+          <t>426650; 473937</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>179994</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>284513</t>
+          <t>307533</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>464507</t>
+          <t>503276</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>171716; 191035</t>
+          <t>171313; 190789</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>228793; 243440</t>
+          <t>230019; 243683</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230513; 245677</t>
+          <t>230588; 245549</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>165908; 192139</t>
+          <t>181690; 211035</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>286994; 311341</t>
+          <t>286407; 310181</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>368755; 383400</t>
+          <t>368176; 383240</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>374482; 392297</t>
+          <t>373228; 391234</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>270246; 297632</t>
+          <t>292603; 322168</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>465485; 496329</t>
+          <t>467599; 497282</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>604345; 623912</t>
+          <t>602749; 623370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>611449; 633949</t>
+          <t>611285; 633817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>445883; 481664</t>
+          <t>483633; 524949</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1104702</t>
+          <t>1162000</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1564793</t>
+          <t>1483525</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2669494</t>
+          <t>2645524</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1395138; 1511228</t>
+          <t>1400719; 1511926</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1787734; 1905940</t>
+          <t>1781529; 1911230</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1629433; 1743343</t>
+          <t>1624172; 1744035</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>851461; 1212100</t>
+          <t>1106345; 1221352</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1987034; 2098254</t>
+          <t>1983020; 2093417</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2344188; 2461200</t>
+          <t>2343467; 2459148</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2119804; 2232713</t>
+          <t>2111362; 2229526</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1412102; 1968520</t>
+          <t>1433536; 1533086</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3411780; 3578155</t>
+          <t>3414949; 3578136</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4171772; 4338291</t>
+          <t>4164479; 4334381</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3775991; 3938798</t>
+          <t>3777097; 3939736</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2428411; 3056824</t>
+          <t>2567115; 2736520</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
